--- a/reports/pdf_change_20260820.xlsx
+++ b/reports/pdf_change_20260820.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,20 +38,37 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -58,16 +77,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="00DCE6F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F2"/>
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000070C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -75,11 +114,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -90,10 +143,39 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 1/7  ·  대기: KoAct, KoAct, TIME, TIME, PLUS, TIGER</t>
+          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 137억(3.0%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -506,102 +588,398 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-    </row>
-    <row r="13" ht="19" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 4억(0.8%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>HPSP  (신규)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>4757370000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.06%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0→100</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-886307400</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.82%→0.56%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>253→187</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>하림지주</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>477621210</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>0.59%→0.71%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>244→287</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-1752627600</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>1.48%→1.01%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>165→119</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>946269000</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.25%→1.52%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>222→258</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-45</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-450648900</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.70%→0.59%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>308→263</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>947830500</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>5.94%→6.35%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>87→90</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-462828600</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.49%→0.39%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>62→49</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-918890700</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>6.18%→6.08%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>398→385</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-321460800</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>0.58%→0.51%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>65→57</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-940751700</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>2.30%→2.07%</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>76→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-899424000</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>6.59%→6.53%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>201→195</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-453876000</v>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>0.62%→0.53%</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>31→26</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -615,18 +993,518 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
     </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="8" t="n"/>
+      <c r="J23" s="8" t="n"/>
+      <c r="K23" s="8" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>221</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>4448288000</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1.81%→3.85%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>200→421</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>고영  (편출)</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-1998588000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>0.90%→0.00%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>194→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>187</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>4469674000</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.53%→3.67%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>151→338</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-6212208000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>3.86%→1.01%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>250→66</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>67</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>4421598000</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>13.63%→15.58%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>453→520</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-4437000000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>6.29%→4.25%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>389→264</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>3358656000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>2.69%→4.25%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>100→156</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-1921272000</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>0.87%→0.00%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-896274000</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.41%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>203→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-221680000</v>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.15%</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>199→119</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="n"/>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-677705000</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>0.68%→0.38%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>150→83</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-439807000</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.29%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>101→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-222343000</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>0.16%→0.06%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>46→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n"/>
+      <c r="C35" s="20" t="n"/>
+      <c r="D35" s="20" t="n"/>
+      <c r="E35" s="20" t="n"/>
+      <c r="F35" s="20" t="n"/>
+      <c r="G35" s="20" t="n"/>
+      <c r="H35" s="20" t="n"/>
+      <c r="I35" s="20" t="n"/>
+      <c r="J35" s="20" t="n"/>
+      <c r="K35" s="20" t="n"/>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="20" t="n"/>
+      <c r="F40" s="20" t="n"/>
+      <c r="G40" s="20" t="n"/>
+      <c r="H40" s="20" t="n"/>
+      <c r="I40" s="20" t="n"/>
+      <c r="J40" s="20" t="n"/>
+      <c r="K40" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="16">
+    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:K35"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260820.xlsx
+++ b/reports/pdf_change_20260820.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 137억(3.0%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -979,7 +979,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1003,7 +1003,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1027,7 +1027,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>

--- a/reports/pdf_change_20260820.xlsx
+++ b/reports/pdf_change_20260820.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>100</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4757370000</v>
+        <v>4752800000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-66</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-886307400</v>
+        <v>-885456000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>43</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>477621210</v>
+        <v>477162400</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-46</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1752627600</v>
+        <v>-1750944000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>946269000</v>
+        <v>945360000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-45</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-450648900</v>
+        <v>-450216000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>947830500</v>
+        <v>946920000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-462828600</v>
+        <v>-918008000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.39%</t>
+          <t>6.18%→6.08%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>62→49</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-918890700</v>
+        <v>-462384000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>6.18%→6.08%</t>
+          <t>0.49%→0.39%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>62→49</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         <v>-8</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-321460800</v>
+        <v>-321152000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>-7</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-940751700</v>
+        <v>-939848000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-899424000</v>
+        <v>-898560000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-453876000</v>
+        <v>-453440000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1003,7 +1003,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1027,7 +1027,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 4종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1449,7 +1449,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>

--- a/reports/pdf_change_20260820.xlsx
+++ b/reports/pdf_change_20260820.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1430,80 +1430,314 @@
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="20" t="n"/>
-      <c r="D35" s="20" t="n"/>
-      <c r="E35" s="20" t="n"/>
-      <c r="F35" s="20" t="n"/>
-      <c r="G35" s="20" t="n"/>
-      <c r="H35" s="20" t="n"/>
-      <c r="I35" s="20" t="n"/>
-      <c r="J35" s="20" t="n"/>
-      <c r="K35" s="20" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 7억(2.6%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 3종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>41847120</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>0.27%→0.42%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>122→191</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-24858080</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.51%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>227→193</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>42332000</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>0.16%→0.31%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>51→101</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-46512000</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>7.97%→7.81%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>761→745</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>58770800</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.21%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>0→11</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-48571600</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>0.48%→0.30%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>30→19</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-40424400</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>1.99%→1.85%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="19" t="inlineStr">
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n"/>
-      <c r="C40" s="20" t="n"/>
-      <c r="D40" s="20" t="n"/>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="20" t="n"/>
-      <c r="G40" s="20" t="n"/>
-      <c r="H40" s="20" t="n"/>
-      <c r="I40" s="20" t="n"/>
-      <c r="J40" s="20" t="n"/>
-      <c r="K40" s="20" t="n"/>
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+      <c r="G46" s="20" t="n"/>
+      <c r="H46" s="20" t="n"/>
+      <c r="I46" s="20" t="n"/>
+      <c r="J46" s="20" t="n"/>
+      <c r="K46" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A37:K37"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A43:K43"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A16:K16"/>
     <mergeCell ref="A19:K19"/>
+    <mergeCell ref="G36:K36"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="G23:K23"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A44:K44"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_change_20260820.xlsx
+++ b/reports/pdf_change_20260820.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-918008000</v>
+        <v>-462384000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>6.18%→6.08%</t>
+          <t>0.49%→0.39%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>62→49</t>
         </is>
       </c>
     </row>
@@ -844,23 +844,23 @@
       <c r="E10" s="17" t="n"/>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-462384000</v>
+        <v>-918008000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.49%→0.39%</t>
+          <t>6.18%→6.08%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>62→49</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 7억(2.6%)      당일 2026-08-20  vs  전영업일 2026-08-19      매수 3종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억      당일 2026-08-20  vs  전영업일 2026-08-19      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
